--- a/results/auto_Cape_Town_Museums_and_Heritage.xlsx
+++ b/results/auto_Cape_Town_Museums_and_Heritage.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Organisation Name</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>021 413 4200</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -423,6 +426,9 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
